--- a/results/Supplementary_Table_7_OddsRatioTest_interesting_hits.xlsx
+++ b/results/Supplementary_Table_7_OddsRatioTest_interesting_hits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/calvin/orb-selection/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A1CA56-2D06-0B42-A82C-8F237F4B23AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B8F1C3-780E-4242-84DD-B68071339828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8640" yWindow="600" windowWidth="23760" windowHeight="22580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
